--- a/data/decontamination/phylogenomic_sets/contaminant_contigs_summary.xlsx
+++ b/data/decontamination/phylogenomic_sets/contaminant_contigs_summary.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/linweili/Important_files/Tables/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/linweili/Important_files/课题进展/Asgard_Eukaryote_Data/data/decontamination/phylogenomic_sets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E94D9BC4-C053-D34B-9466-1D20FDA97AB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A047DDA-9CC0-DD40-B62D-2FDDEE4852CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2240" yWindow="-19480" windowWidth="27640" windowHeight="16920" xr2:uid="{0F6A6B91-30A4-6D44-B2C4-7418DAB2922F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -117,10 +117,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -496,7 +497,7 @@
       <c r="D2" s="1">
         <v>7318</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="3">
         <f>D2/C2*100</f>
         <v>4.5299790771668746</v>
       </c>
@@ -514,7 +515,7 @@
       <c r="D3" s="1">
         <v>2661</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="3">
         <f>D3/C3*100</f>
         <v>4.1237912224150755</v>
       </c>
@@ -533,7 +534,7 @@
         <f>7734+3047</f>
         <v>10781</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="3">
         <f>D4/C4*100</f>
         <v>4.9145055636342088</v>
       </c>
@@ -551,7 +552,7 @@
       <c r="D5" s="1">
         <v>3074</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="3">
         <f>D5/C5*100</f>
         <v>4.2365523229371957</v>
       </c>
@@ -569,7 +570,7 @@
       <c r="D6" s="1">
         <v>7053</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="3">
         <f>D6/C6*100</f>
         <v>5.10894445571234</v>
       </c>
